--- a/问题2/口径对照_读法与终端与效率.xlsx
+++ b/问题2/口径对照_读法与终端与效率.xlsx
@@ -774,13 +774,13 @@
         <v>73</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>711.1297</v>
+        <v>479.312</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>766.9992999999999</v>
+        <v>558.3117</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>55.8697</v>
+        <v>78.9997</v>
       </c>
     </row>
     <row r="4">
@@ -822,13 +822,13 @@
         <v>97</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>612.6781999999999</v>
+        <v>562.2616</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>677.5717</v>
+        <v>507.3242</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>64.8935</v>
+        <v>-54.9374</v>
       </c>
     </row>
     <row r="6">
@@ -846,13 +846,13 @@
         <v>109</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>680.0029</v>
+        <v>697.9973</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>720.4549</v>
+        <v>682.3533</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>40.452</v>
+        <v>-15.644</v>
       </c>
     </row>
     <row r="7">
@@ -966,13 +966,13 @@
         <v>97</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>369.8762</v>
+        <v>78.5716</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>415.1474</v>
+        <v>27.005</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>45.2713</v>
+        <v>-51.5666</v>
       </c>
     </row>
     <row r="12">
@@ -990,13 +990,13 @@
         <v>109</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>606.8636</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>693.3593</v>
+        <v>385.9017</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>86.4957</v>
+        <v>385.9017</v>
       </c>
     </row>
     <row r="13">
@@ -1062,13 +1062,13 @@
         <v>73</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0</v>
+        <v>354.1946</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0</v>
+        <v>380.0212</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0</v>
+        <v>25.8266</v>
       </c>
     </row>
     <row r="16">
@@ -1110,13 +1110,13 @@
         <v>97</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>47.7433</v>
+        <v>589.4326</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>90.84229999999999</v>
+        <v>493.5825</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>43.099</v>
+        <v>-95.8501</v>
       </c>
     </row>
     <row r="18">
@@ -1134,13 +1134,13 @@
         <v>109</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>52.758</v>
+        <v>764.3298</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>627.2015</v>
+        <v>752.645</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>574.4435</v>
+        <v>-11.6848</v>
       </c>
     </row>
     <row r="19">
@@ -1206,13 +1206,13 @@
         <v>73</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>726.9715</v>
+        <v>932.828</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>729.9462</v>
+        <v>906.6833</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>2.9746</v>
+        <v>-26.1447</v>
       </c>
     </row>
     <row r="22">
@@ -1254,13 +1254,13 @@
         <v>97</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>714.0086</v>
+        <v>801.3819</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>796.6044000000001</v>
+        <v>795.9304</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>82.5958</v>
+        <v>-5.4514</v>
       </c>
     </row>
     <row r="24">
@@ -1278,13 +1278,13 @@
         <v>109</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>710.1420000000001</v>
+        <v>715.4144</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>727.9246000000001</v>
+        <v>712.6333</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>17.7827</v>
+        <v>-2.7811</v>
       </c>
     </row>
     <row r="25">
